--- a/光伏配储项目/电价数据/2026/汕头厂.xlsx
+++ b/光伏配储项目/电价数据/2026/汕头厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.29398</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.25515</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07479999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.73375</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.62697</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17769</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.61978</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6699400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.58109</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.8202</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.85248</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.67171</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.50678</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.77734</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.02082</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6915399999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.06877</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.4594</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.04362</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.03607</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.37488</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.26381</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.79741</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8724700000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.98983</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6715099999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8269</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57885</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.66243</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.31349</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.11015</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.09426000000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.10302</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.10091</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.11188</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.21037</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.12871</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.23926</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5571200000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.70497</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6516799999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6280800000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5665</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.94921</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.81617</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.9505800000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5639299999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.47663</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.53331</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.8651799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.20723</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.82821</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.93879</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8636900000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.08115</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.48301</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.12205</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.02727</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.11106</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.02768</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.15804</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.96417</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.05626</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.96104</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.07564</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9278500000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.86225</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9976499999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9978400000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.54895</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.94037</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.72466</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.5465099999999999</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.50964</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.5435099999999999</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.317</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.22424</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.23629</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.18441</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.21044</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.23929</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.25675</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.27581</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.24247</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.23141</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.14242</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.22263</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.78838</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7879299999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.38076</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.91072</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.86807</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.6658200000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.00146</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.6910700000000001</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.48389</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.49264</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5385599999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.49666</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.41403</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.68933</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.48407</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5714199999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.84157</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57438</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.81516</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.43009</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47996</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50141</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.66422</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.69652</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.57711</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.27167</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.32591</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.22046</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.47763</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.009800000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79208</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.10451</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6578999999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50231</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13333</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25476</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23089</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09693</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03354</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3177</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19474</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25253</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2164</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19435</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17602</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20301</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26774</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.0304</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.03801</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.004160000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2016</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04445</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.18944</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.004730000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31648</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.76281</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5729099999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.20046</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.24101</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.25584</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18126</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32452</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7950900000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.15621</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.13414</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45361</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.05736</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.61539</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.58956</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.63407</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.63995</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.67889</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.73725</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.62442</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.5957899999999999</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.6723600000000001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.61764</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.6855399999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.67022</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.50985</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.6316499999999999</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.5350199999999999</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.62498</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.62879</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.61956</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.5819500000000001</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.6072000000000001</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.61917</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.61172</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.58284</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.62502</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.63491</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.65377</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.6453300000000001</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.62464</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.48043</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.85588</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.6698500000000001</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.83257</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.48936</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5002</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.50074</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.89166</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.79747</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44363</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.25417</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.20674</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.10271</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.24323</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.00624</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.60905</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.51701</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5137999999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.47454</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.55352</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.64379</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.56345</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.51677</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.52186</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.57297</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.5664600000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.5761799999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.48263</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.5357499999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.48643</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.54849</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.49044</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.4352200000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.48038</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18788</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18499</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.49028</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03937</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18725</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.0424</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.58065</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.49553</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28175</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30394</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.04165</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.63561</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48503</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49666</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44455</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48426</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.26704</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.08702</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41587</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>-0.01853</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.5614400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.12362</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.20946</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20039</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19084</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27372</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19351</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15512</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23577</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19108</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20377</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16871</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.5399400000000001</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.63058</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.60423</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.40301</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32375</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.01119</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27441</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.50666</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29784</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.56804</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60288</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7562300000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3148</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43212</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46196</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.49367</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.62198</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64337</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.7192000000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6788099999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.54892</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64712</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32418</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.67245</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.69101</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5471699999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.79669</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.59494</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.54113</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.54283</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.54496</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.53818</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16872</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00014</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16828</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.01137</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20064</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16872</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.00242</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15833</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16052</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16599</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.00364</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16872</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.00378</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.02864</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17965</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18327</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.02433</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.15864</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.16418</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.22792</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21641</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.5183099999999999</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24681</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23167</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18809</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18485</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.01041</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20431</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01043</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01043</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01061</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.02451</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01083</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17629</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.02415</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.02417</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.009810000000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01128</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24448</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02862</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00756</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-5.999999999999999e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02168</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02674</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.06864000000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.18825</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.01798</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01026</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26914</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17023</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16507</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16942</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.03474</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16293</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15168</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.03437</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.03409</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.00446</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.00282</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19406</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.03544</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23621</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85317</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8573999999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08331000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01369</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.50275</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00179</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6359900000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.73452</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.68522</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.73176</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.73176</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.73092</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.81129</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31012</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19262</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24773</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21642</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25922</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20288</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19848</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16292</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16527</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.03473</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18287</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23364</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26148</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.21529</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.22471</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26078</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.294</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.56028</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46125</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44731</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46289</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.74603</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.75164</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5051100000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.76722</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31799</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.67953</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46606</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5136799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.67687</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.78152</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.67965</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55949</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32492</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.03412</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.50712</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19907</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51803</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5043500000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5866699999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33021</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6678500000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46981</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.45698</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3406</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17911</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20103</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14198</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11604</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14575</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14321</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18824</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23002</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.49592</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.46267</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22346</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.54001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.52418</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.64032</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46816</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.35672</v>
       </c>
     </row>
   </sheetData>
